--- a/beeld_hk/data_hk.xlsx
+++ b/beeld_hk/data_hk.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eigenaar\Documents\quarto_presentaties\beeld_hk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0B7FCE-5183-4785-82B3-C70A4F0D4EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48AF9F5-3BC2-429D-A7E0-6056DF7AD655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{47BE33E6-191F-4FEC-BB35-FE95ED45CF00}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{47BE33E6-191F-4FEC-BB35-FE95ED45CF00}"/>
   </bookViews>
   <sheets>
     <sheet name="transit" sheetId="1" r:id="rId1"/>
     <sheet name="verdichtung" sheetId="2" r:id="rId2"/>
     <sheet name="GP" sheetId="4" r:id="rId3"/>
+    <sheet name="dichte" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="46">
   <si>
     <t>datum</t>
   </si>
@@ -116,6 +117,66 @@
   </si>
   <si>
     <t>Dichte</t>
+  </si>
+  <si>
+    <t>49.5</t>
+  </si>
+  <si>
+    <t>2.89</t>
+  </si>
+  <si>
+    <t>3.13</t>
+  </si>
+  <si>
+    <t>28.2</t>
+  </si>
+  <si>
+    <t>2.43</t>
+  </si>
+  <si>
+    <t>3.29</t>
+  </si>
+  <si>
+    <t>25.9</t>
+  </si>
+  <si>
+    <t>2.56</t>
+  </si>
+  <si>
+    <t>3.26</t>
+  </si>
+  <si>
+    <t>17.0</t>
+  </si>
+  <si>
+    <t>2.58</t>
+  </si>
+  <si>
+    <t>2.73</t>
+  </si>
+  <si>
+    <t>41.0</t>
+  </si>
+  <si>
+    <t>2.69</t>
+  </si>
+  <si>
+    <t>2.85</t>
+  </si>
+  <si>
+    <t>41.1</t>
+  </si>
+  <si>
+    <t>2.75</t>
+  </si>
+  <si>
+    <t>perc_korner</t>
+  </si>
+  <si>
+    <t>hohe</t>
+  </si>
+  <si>
+    <t>dichte</t>
   </si>
 </sst>
 </file>
@@ -1029,4 +1090,157 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C235D507-A96D-4E9A-8926-8EAF8A8119D8}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13">
+        <v>274</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>